--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486487_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486487_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1138</v>
+        <v>6.6571</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7622</v>
+        <v>4.874</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3516</v>
+        <v>1.7831</v>
       </c>
       <c r="G2" t="n">
         <v>4.6981</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0257</v>
+        <v>0.569</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0721</v>
+        <v>0.1839</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0464</v>
+        <v>0.3851</v>
       </c>
       <c r="V2" t="n">
         <v>2.2599</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3686</v>
+        <v>4.4576</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6083</v>
+        <v>2.8405</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7603</v>
+        <v>1.6171</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7786</v>
+        <v>2.0142</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6408</v>
+        <v>3.0231</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8623</v>
+        <v>-1.0088</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3596</v>
+        <v>2.9554</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5676</v>
+        <v>2.6279</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2079</v>
+        <v>0.3275</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.9412</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0732</v>
+        <v>0.3951</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6543</v>
+        <v>-1.3364</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>3.4596</v>
+        <v>0.2911</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0333</v>
+        <v>-0.1574</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4263</v>
+        <v>0.4485</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.3045</v>
+        <v>1.4997</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.695</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0414</v>
+        <v>2.5767</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3934</v>
+        <v>1.1554</v>
       </c>
       <c r="F4" t="n">
-        <v>1.648</v>
+        <v>1.4213</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0142</v>
+        <v>1.7786</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0231</v>
+        <v>3.6408</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0088</v>
+        <v>-1.8623</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9554</v>
+        <v>2.3596</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6279</v>
+        <v>2.5676</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3275</v>
+        <v>-0.2079</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9412</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3951</v>
+        <v>1.0732</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3364</v>
+        <v>-1.6543</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1251</v>
+        <v>1.6677</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6044</v>
+        <v>0.5804</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4793</v>
+        <v>1.0872</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4997</v>
+        <v>-1.3045</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3698</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9398</v>
+        <v>1.465</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0716</v>
+        <v>3.0283</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1318</v>
+        <v>-1.5633</v>
       </c>
       <c r="G5" t="n">
         <v>2.0598</v>
@@ -844,13 +844,13 @@
         <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7277</v>
+        <v>0.253</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1971</v>
+        <v>0.1538</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1952</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6309</v>
+        <v>0.3419</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9612</v>
+        <v>-1.8495</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5921</v>
+        <v>2.1914</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2925</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9658</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1454</v>
+        <v>-0.0336</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1112</v>
+        <v>0.7105</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1817</v>
+        <v>0.2009</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.08</v>
+        <v>0.0318</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2616</v>
+        <v>0.1692</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5157</v>
@@ -1000,13 +1000,13 @@
         <v>1.5225</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0019</v>
+        <v>1.0211</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1406</v>
+        <v>0.2524</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8612</v>
+        <v>0.7688</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7395</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. AYESA RODRIGUEZ</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9711</v>
+        <v>-0.6921</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2183</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2472</v>
+        <v>-0.1069</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0257</v>
+        <v>-0.1667</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.362</v>
+        <v>2.1928</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3363</v>
+        <v>-2.3595</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0747</v>
+        <v>-0.173</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0365</v>
+        <v>1.3171</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0382</v>
+        <v>-1.4901</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1004</v>
+        <v>0.0063</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3985</v>
+        <v>0.8757</v>
       </c>
       <c r="O8" t="n">
-        <v>0.298</v>
+        <v>-0.8694</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>-0.2175</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.5699</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2055</v>
+        <v>-0.1947</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1301</v>
+        <v>-0.3752</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>M. AYESA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.72</v>
+        <v>-0.8786</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2124</v>
+        <v>-1.2183</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.3397</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1667</v>
+        <v>-0.0257</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1928</v>
+        <v>-0.362</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3595</v>
+        <v>0.3363</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.173</v>
+        <v>0.0747</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3171</v>
+        <v>0.0365</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4901</v>
+        <v>0.0382</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0063</v>
+        <v>-0.1004</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8757</v>
+        <v>-0.3985</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8694</v>
+        <v>0.298</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5979</v>
+        <v>0.0171</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.822</v>
+        <v>-0.2055</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7759</v>
+        <v>0.2226</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0391</v>
+        <v>-2.1633</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7255</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3136</v>
+        <v>-1.2828</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5784</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0479</v>
+        <v>-0.1721</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4831</v>
+        <v>0.3281</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.531</v>
+        <v>-0.5002</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7023</v>
+        <v>-3.0905</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1282</v>
+        <v>-2.948</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.574</v>
+        <v>-0.1425</v>
       </c>
       <c r="G11" t="n">
         <v>-3.728</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.1719</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8359</v>
+        <v>-0.4044</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8364</v>
+        <v>-3.5251</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5989</v>
+        <v>-1.1951</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2375</v>
+        <v>-2.33</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8686</v>
@@ -1390,13 +1390,13 @@
         <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7502</v>
+        <v>-0.4389</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4795</v>
+        <v>-0.0757</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2708</v>
+        <v>-0.3632</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.007299999999999</v>
+        <v>5.349599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.911</v>
+        <v>3.253399999999999</v>
       </c>
       <c r="F13" t="n">
         <v>2.096299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.375099999999998</v>
+        <v>1.3751</v>
       </c>
       <c r="H13" t="n">
         <v>15.0851</v>
@@ -1468,10 +1468,10 @@
         <v>13.0504</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>3.0825</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6610000000000003</v>
+        <v>1.0036</v>
       </c>
       <c r="U13" t="n">
         <v>2.0788</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>J. MWEMA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3596</v>
+        <v>3.6738</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6917</v>
+        <v>3.94</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6679</v>
+        <v>-0.2662</v>
       </c>
       <c r="G14" t="n">
-        <v>3.275</v>
+        <v>4.8027</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3259</v>
+        <v>-0.3713</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9491</v>
+        <v>5.174</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8672</v>
+        <v>4.2969</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0257</v>
+        <v>0.146</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8415</v>
+        <v>4.1509</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4078</v>
+        <v>0.5058</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6998</v>
+        <v>-0.5173</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1076</v>
+        <v>1.0231</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7372</v>
+        <v>-0.5438</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7169</v>
+        <v>-0.3569</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0203</v>
+        <v>-0.1869</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.8902</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1952</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MWEMA</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9416</v>
+        <v>3.5991</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2694</v>
+        <v>3.1213</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3278</v>
+        <v>0.4778</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8027</v>
+        <v>3.275</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3713</v>
+        <v>1.3259</v>
       </c>
       <c r="I15" t="n">
-        <v>5.174</v>
+        <v>1.9491</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2969</v>
+        <v>2.8672</v>
       </c>
       <c r="K15" t="n">
-        <v>0.146</v>
+        <v>2.0257</v>
       </c>
       <c r="L15" t="n">
-        <v>4.1509</v>
+        <v>0.8415</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5058</v>
+        <v>0.4078</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5173</v>
+        <v>-0.6998</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0231</v>
+        <v>1.1076</v>
       </c>
       <c r="P15" t="n">
-        <v>1.305</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.276</v>
+        <v>0.9767</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0274</v>
+        <v>1.1464</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2485</v>
+        <v>-0.1698</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8902</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8902</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2525</v>
+        <v>1.9539</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4352</v>
+        <v>0.2353</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6877</v>
+        <v>1.7186</v>
       </c>
       <c r="G16" t="n">
         <v>-0.023</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7245</v>
+        <v>-0.0231</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.0829</v>
       </c>
       <c r="U16" t="n">
-        <v>0.029</v>
+        <v>0.0598</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9661</v>
+        <v>1.1463</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1457</v>
+        <v>-0.2781</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1796</v>
+        <v>1.4244</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1008</v>
+        <v>1.495</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0697</v>
+        <v>-1.1465</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0311</v>
+        <v>2.6416</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3154</v>
+        <v>0.8737</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1592</v>
+        <v>-0.4467</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1562</v>
+        <v>1.3204</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4162</v>
+        <v>0.6214</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2289</v>
+        <v>-0.6998</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1873</v>
+        <v>1.3212</v>
       </c>
       <c r="P17" t="n">
-        <v>0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1283</v>
+        <v>-0.4119</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4074</v>
+        <v>-0.1274</v>
       </c>
       <c r="U17" t="n">
-        <v>0.279</v>
+        <v>-0.2845</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3252</v>
+        <v>1.1507</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3252</v>
+        <v>1.1507</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8303</v>
+        <v>0.8042</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5016</v>
+        <v>0.9222</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3319</v>
+        <v>-0.118</v>
       </c>
       <c r="G18" t="n">
-        <v>1.495</v>
+        <v>-1.1008</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1465</v>
+        <v>-0.0697</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6416</v>
+        <v>-1.0311</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8737</v>
+        <v>1.3154</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.4467</v>
+        <v>1.1592</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3204</v>
+        <v>0.1562</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6214</v>
+        <v>-2.4162</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6998</v>
+        <v>-1.2289</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3212</v>
+        <v>-1.1873</v>
       </c>
       <c r="P18" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7279</v>
+        <v>-0.2902</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3509</v>
+        <v>-0.6309</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.377</v>
+        <v>0.3407</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1507</v>
+        <v>1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1507</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2639</v>
+        <v>-0.2331</v>
       </c>
       <c r="E19" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1954</v>
+        <v>-0.1646</v>
       </c>
       <c r="G19" t="n">
         <v>-0.067</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.197</v>
+        <v>-0.1661</v>
       </c>
       <c r="T19" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>J. BONE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1072</v>
+        <v>-1.5087</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0573</v>
+        <v>-2.2027</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0499</v>
+        <v>0.694</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4363</v>
+        <v>-1.1632</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2505</v>
+        <v>-3.7562</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1857</v>
+        <v>2.593</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4719</v>
+        <v>-0.9566</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4536</v>
+        <v>-2.1439</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0183</v>
+        <v>1.1873</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9643</v>
+        <v>-0.2066</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-1.6123</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1674</v>
+        <v>1.4056</v>
       </c>
       <c r="P20" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4591</v>
+        <v>-0.7805</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4146</v>
+        <v>-0.1586</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0445</v>
+        <v>-0.6219</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>A. JORDA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4179</v>
+        <v>-1.6995</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8828</v>
+        <v>-0.8356</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5351</v>
+        <v>-0.8639</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0703</v>
+        <v>-0.3016</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8368</v>
+        <v>-0.9399</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2335</v>
+        <v>0.6383</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4719</v>
+        <v>1.8141</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4719</v>
+        <v>0.073</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.7412</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5985</v>
+        <v>-2.1158</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.365</v>
+        <v>-1.0129</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2335</v>
+        <v>-1.1029</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3699</v>
+        <v>-0.3103</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.411</v>
+        <v>-0.4747</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0411</v>
+        <v>0.1643</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. JORDA RODRIGUEZ</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4612</v>
+        <v>-2.1817</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1709</v>
+        <v>-1.2809</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2903</v>
+        <v>-0.9009</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3016</v>
+        <v>-3.4363</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9399</v>
+        <v>-2.2505</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6383</v>
+        <v>-1.1857</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8141</v>
+        <v>-1.4719</v>
       </c>
       <c r="K22" t="n">
-        <v>0.073</v>
+        <v>-1.4536</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7412</v>
+        <v>-0.0183</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1158</v>
+        <v>-1.9643</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0129</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1029</v>
+        <v>-1.1674</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.072</v>
+        <v>0.3845</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8099</v>
+        <v>0.1911</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2621</v>
+        <v>0.1935</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. BONE</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6995</v>
+        <v>-2.3563</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2085</v>
+        <v>-1.8828</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5091</v>
+        <v>-0.4734</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1632</v>
+        <v>-2.0703</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.7562</v>
+        <v>-1.8368</v>
       </c>
       <c r="I23" t="n">
-        <v>2.593</v>
+        <v>-0.2335</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9566</v>
+        <v>-1.4719</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1439</v>
+        <v>-1.4719</v>
       </c>
       <c r="L23" t="n">
-        <v>1.1873</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2066</v>
+        <v>-0.5985</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6123</v>
+        <v>-0.365</v>
       </c>
       <c r="O23" t="n">
-        <v>1.4056</v>
+        <v>-0.2335</v>
       </c>
       <c r="P23" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9713</v>
+        <v>-0.3082</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1644</v>
+        <v>-0.411</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8068</v>
+        <v>0.1027</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2631</v>
+        <v>-3.1063</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6922</v>
+        <v>-1.4687</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5709</v>
+        <v>-1.6377</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8125</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1679</v>
+        <v>-0.0111</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6044</v>
+        <v>-0.3809</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4366</v>
+        <v>0.3698</v>
       </c>
       <c r="V24" t="n">
         <v>-0.7602</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1446</v>
+        <v>-4.3539</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.186</v>
+        <v>-2.2978</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9586</v>
+        <v>-2.0562</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9732</v>
@@ -2404,13 +2404,13 @@
         <v>1.9576</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3014</v>
+        <v>-0.5107</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6128</v>
+        <v>-0.7246</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3115</v>
+        <v>0.2139</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5649999999999999</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.007299999999998</v>
+        <v>-4.2622</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.096200000000001</v>
+        <v>-2.0963</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.911</v>
+        <v>-2.166100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-1.375200000000001</v>
@@ -2470,7 +2470,7 @@
         <v>-9.6435</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3987000000000003</v>
+        <v>-0.3986999999999989</v>
       </c>
       <c r="P26" t="n">
         <v>-1.0875</v>
@@ -2482,16 +2482,16 @@
         <v>11.9627</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.7399</v>
+        <v>-1.9947</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.0787</v>
+        <v>-2.0789</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6609</v>
+        <v>0.08399999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1952999999999996</v>
+        <v>0.1952999999999998</v>
       </c>
       <c r="W26" t="n">
         <v>4.366099999999999</v>
